--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487841_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487841_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8986</v>
+        <v>4.3727</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1961</v>
+        <v>2.3888</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7025</v>
+        <v>1.9839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2827</v>
+        <v>3.3513</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5178</v>
+        <v>3.2664</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2351</v>
+        <v>0.0849</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9074</v>
+        <v>3.8209</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0037</v>
+        <v>3.7033</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.0963</v>
+        <v>0.1176</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6247</v>
+        <v>-0.4696</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4859</v>
+        <v>-0.4369</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.1388</v>
+        <v>-0.0326</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R2" t="n">
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7616</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0994</v>
+        <v>0.6272</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6623</v>
+        <v>0.0809</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3975</v>
+        <v>0.9376</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.587</v>
+        <v>4.2544</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6031</v>
+        <v>2.9336</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9839</v>
+        <v>1.3208</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3513</v>
+        <v>0.2827</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2664</v>
+        <v>0.5178</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0849</v>
+        <v>-0.2351</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8209</v>
+        <v>0.9074</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7033</v>
+        <v>1.0037</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1176</v>
+        <v>-0.0963</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4696</v>
+        <v>-0.6247</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4369</v>
+        <v>-0.4859</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0326</v>
+        <v>-0.1388</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R3" t="n">
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9225</v>
+        <v>1.1174</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8416</v>
+        <v>0.8368</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0809</v>
+        <v>0.2806</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9376</v>
+        <v>1.3975</v>
       </c>
       <c r="W3" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7076</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4434</v>
+        <v>3.0712</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1845</v>
+        <v>2.6068</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2589</v>
+        <v>0.4644</v>
       </c>
       <c r="G4" t="n">
         <v>-0.029</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0562</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2049</v>
+        <v>0.6272</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1487</v>
+        <v>0.0568</v>
       </c>
       <c r="V4" t="n">
         <v>1.1675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5654</v>
+        <v>2.6217</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7982</v>
+        <v>3.2762</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7672</v>
+        <v>-0.6545</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7429</v>
+        <v>0.7128</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7681</v>
+        <v>-0.6612</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9748</v>
+        <v>1.374</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5425</v>
+        <v>2.6847</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1506</v>
+        <v>0.3513</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6932</v>
+        <v>2.3333</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2004</v>
+        <v>-1.9719</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9187</v>
+        <v>-1.0126</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2817</v>
+        <v>-0.9593</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4974</v>
+        <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9545</v>
+        <v>0.8277</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2544</v>
+        <v>0.5915</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.2362</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1051</v>
+        <v>-0.5838</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.23</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4717</v>
+        <v>2.5388</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6307</v>
+        <v>1.0358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.841</v>
+        <v>1.5029</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1644</v>
+        <v>-1.7429</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1982</v>
+        <v>-0.7681</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3626</v>
+        <v>-0.9748</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6279</v>
+        <v>-0.5425</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0679</v>
+        <v>0.1506</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4401</v>
+        <v>-0.6932</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7922</v>
+        <v>-1.2004</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8697</v>
+        <v>-0.9187</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9225</v>
+        <v>-0.2817</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4568</v>
+        <v>2.4974</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9898</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8135</v>
+        <v>0.492</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1764</v>
+        <v>0.4358</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>2.1051</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>2.3351</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1828</v>
+        <v>1.9393</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9547</v>
+        <v>2.7983</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7719</v>
+        <v>-0.859</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7128</v>
+        <v>0.5452</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6612</v>
+        <v>0.0423</v>
       </c>
       <c r="I7" t="n">
-        <v>1.374</v>
+        <v>0.5029</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6847</v>
+        <v>2.4925</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3513</v>
+        <v>0.961</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3333</v>
+        <v>1.5316</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9719</v>
+        <v>-1.9474</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0126</v>
+        <v>-0.9187</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9593</v>
+        <v>-1.0287</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3888</v>
+        <v>0.9155</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2701</v>
+        <v>1.1164</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1188</v>
+        <v>-0.2009</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5838</v>
+        <v>-0.3538</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
         <v>-0.5838</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8868</v>
+        <v>1.6451</v>
       </c>
       <c r="E8" t="n">
-        <v>1.8339</v>
+        <v>1.3326</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.947</v>
+        <v>0.3125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5452</v>
+        <v>-0.1644</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0423</v>
+        <v>1.1982</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5029</v>
+        <v>-1.3626</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4925</v>
+        <v>1.6279</v>
       </c>
       <c r="K8" t="n">
-        <v>0.961</v>
+        <v>2.0679</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5316</v>
+        <v>-0.4401</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9474</v>
+        <v>-1.7922</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9187</v>
+        <v>-0.8697</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0287</v>
+        <v>-0.9225</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8731</v>
+        <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.137</v>
+        <v>1.1632</v>
       </c>
       <c r="T8" t="n">
-        <v>0.152</v>
+        <v>0.5153</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.289</v>
+        <v>0.6479</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3538</v>
+        <v>0.23</v>
       </c>
       <c r="W8" t="n">
         <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>N. RAKOCEVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8505</v>
+        <v>1.3867</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7571</v>
+        <v>0.5713</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0934</v>
+        <v>0.8153</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3487</v>
+        <v>-0.5112</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.516</v>
+        <v>-0.6801</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8647</v>
+        <v>0.169</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7323</v>
+        <v>0.5218</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5609</v>
+        <v>0.2834</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2932</v>
+        <v>0.2384</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6163999999999999</v>
+        <v>-1.0329</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0449</v>
+        <v>-0.9636</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5715</v>
+        <v>-0.0694</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1631</v>
+        <v>0.6491</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0248</v>
+        <v>0.2577</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1879</v>
+        <v>0.3915</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. RAKOCEVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7232</v>
+        <v>1.1697</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1427</v>
+        <v>0.9295</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5805</v>
+        <v>0.2402</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5112</v>
+        <v>1.3487</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6801</v>
+        <v>-0.516</v>
       </c>
       <c r="I10" t="n">
-        <v>0.169</v>
+        <v>1.8647</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5218</v>
+        <v>0.7323</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2834</v>
+        <v>-0.5609</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2384</v>
+        <v>1.2932</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0329</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9636</v>
+        <v>0.0449</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0694</v>
+        <v>0.5715</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4568</v>
+        <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0144</v>
+        <v>0.1561</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.171</v>
+        <v>0.1972</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1566</v>
+        <v>-0.0411</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4918</v>
+        <v>1.145</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2254</v>
+        <v>1.7611</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7335</v>
+        <v>-0.6161</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6451</v>
@@ -1312,13 +1312,13 @@
         <v>1.0406</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1951</v>
+        <v>0.4581</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0281</v>
+        <v>0.5077</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.167</v>
+        <v>-0.0496</v>
       </c>
       <c r="V11" t="n">
         <v>1.2914</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.4442</v>
+        <v>-5.8351</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5335</v>
+        <v>-2.1887</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9107</v>
+        <v>-3.6464</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5148</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0106</v>
+        <v>-0.4016</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7581</v>
+        <v>-0.4133</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2525</v>
+        <v>0.0118</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9188</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.657</v>
+        <v>18.3095</v>
       </c>
       <c r="E13" t="n">
-        <v>16.7929</v>
+        <v>17.4453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8643000000000005</v>
+        <v>0.8639999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3666999999999998</v>
@@ -1444,7 +1444,7 @@
         <v>12.6163</v>
       </c>
       <c r="K13" t="n">
-        <v>5.880800000000001</v>
+        <v>5.880799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>6.735300000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-7.4925</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.490399999999999</v>
+        <v>-5.4904</v>
       </c>
       <c r="P13" t="n">
         <v>9.3652</v>
@@ -1468,16 +1468,16 @@
         <v>16.6493</v>
       </c>
       <c r="S13" t="n">
-        <v>6.553199999999999</v>
+        <v>7.2056</v>
       </c>
       <c r="T13" t="n">
-        <v>4.7035</v>
+        <v>5.355699999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.85</v>
+        <v>1.8499</v>
       </c>
       <c r="V13" t="n">
-        <v>2.105199999999999</v>
+        <v>2.1052</v>
       </c>
       <c r="W13" t="n">
         <v>6.7576</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2482</v>
+        <v>1.7291</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1982</v>
+        <v>1.3053</v>
       </c>
       <c r="F14" t="n">
-        <v>0.05</v>
+        <v>0.4238</v>
       </c>
       <c r="G14" t="n">
         <v>1.4099</v>
@@ -1546,13 +1546,13 @@
         <v>0.2081</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3699</v>
+        <v>0.1111</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0216</v>
+        <v>0.3954</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0204</v>
+        <v>1.3648</v>
       </c>
       <c r="E15" t="n">
-        <v>0.925</v>
+        <v>0.4964</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0954</v>
+        <v>0.8685</v>
       </c>
       <c r="G15" t="n">
         <v>1.1365</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3242</v>
+        <v>0.0202</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2048</v>
+        <v>-0.2238</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5291</v>
+        <v>0.244</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6441</v>
+        <v>0.3123</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1691</v>
+        <v>0.5262</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5251</v>
+        <v>-0.2139</v>
       </c>
       <c r="G16" t="n">
         <v>0.188</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.456</v>
+        <v>0.1243</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9192</v>
+        <v>0.2763</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4631</v>
+        <v>-0.152</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W. NIANG</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5486</v>
+        <v>-0.2174</v>
       </c>
       <c r="E17" t="n">
+        <v>-0.8162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.5213</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.0878</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.2806</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.4162</v>
       </c>
-      <c r="F17" t="n">
-        <v>-0.9648</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-2.6319</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-2.6205</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-0.0114</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-0.068</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-1.2649</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.1969</v>
-      </c>
-      <c r="M17" t="n">
-        <v>-2.5639</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-1.3556</v>
-      </c>
       <c r="O17" t="n">
-        <v>-1.2083</v>
+        <v>-0.1755</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4162</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6858</v>
+        <v>0.1344</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9192</v>
+        <v>-0.0157</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.1501</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>I. MONTERO MECA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4484</v>
+        <v>-0.9909</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2449</v>
+        <v>0.3498</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2036</v>
+        <v>-1.3407</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5213</v>
+        <v>0.6187</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0878</v>
+        <v>0.6293</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4335</v>
+        <v>-0.0106</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2806</v>
+        <v>1.3824</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6716</v>
+        <v>0.9358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.609</v>
+        <v>0.4465</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2407</v>
+        <v>-0.7637</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4162</v>
+        <v>-0.3065</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1755</v>
+        <v>-0.4572</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8731</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>-3.3299</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0967</v>
+        <v>-0.8633999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4443</v>
+        <v>-0.6215000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6524</v>
+        <v>-0.242</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.7513</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. AREVALO SAENZ</t>
+          <t>W. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.715</v>
+        <v>-1.0859</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2403</v>
+        <v>-0.2267</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9553</v>
+        <v>-0.8591</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.9288</v>
+        <v>-2.6319</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6585</v>
+        <v>-2.6205</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2703</v>
+        <v>-0.0114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1943</v>
+        <v>-0.068</v>
       </c>
       <c r="K19" t="n">
-        <v>0.07679999999999999</v>
+        <v>-1.2649</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1176</v>
+        <v>1.1969</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1231</v>
+        <v>-2.5639</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7352</v>
+        <v>-1.3556</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3879</v>
+        <v>-1.2083</v>
       </c>
       <c r="P19" t="n">
         <v>-0.4162</v>
@@ -1936,19 +1936,19 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4626</v>
+        <v>1.1486</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1272</v>
+        <v>0.2763</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3354</v>
+        <v>0.8723</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0.8137</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>A. PLITZUWEIT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1319</v>
+        <v>-1.0863</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1672</v>
+        <v>0.3395</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9648</v>
+        <v>-1.4258</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7846</v>
+        <v>0.2497</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2196</v>
+        <v>0.222</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.0278</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.7357</v>
       </c>
       <c r="K20" t="n">
-        <v>0.552</v>
+        <v>0.2834</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0392</v>
+        <v>0.4523</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3758</v>
+        <v>-0.486</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.0614</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6041</v>
+        <v>-0.4245</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0581</v>
+        <v>-1.0009</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.261</v>
+        <v>-0.3962</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2029</v>
+        <v>-0.6047</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5838</v>
+        <v>-1.1675</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PLITZUWEIT</t>
+          <t>B. AREVALO SAENZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2102</v>
+        <v>-1.599</v>
       </c>
       <c r="E21" t="n">
-        <v>0.018</v>
+        <v>0.1332</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2282</v>
+        <v>-1.7322</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2497</v>
+        <v>-2.9288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.222</v>
+        <v>-1.6585</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0278</v>
+        <v>-1.2703</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7357</v>
+        <v>0.1943</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2834</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4523</v>
+        <v>0.1176</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.486</v>
+        <v>-3.1231</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0614</v>
+        <v>-1.7352</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4245</v>
+        <v>-1.3879</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="R21" t="n">
         <v>0.8325</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.1249</v>
+        <v>0.5785</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7177</v>
+        <v>0.02</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4072</v>
+        <v>0.5585</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1675</v>
+        <v>1.1675</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. MONTERO MECA</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2719</v>
+        <v>-1.9597</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1355</v>
+        <v>-1.1672</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4074</v>
+        <v>-0.7926</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6187</v>
+        <v>-0.7846</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6293</v>
+        <v>-0.2196</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0106</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3824</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9358</v>
+        <v>0.552</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4465</v>
+        <v>0.0392</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7637</v>
+        <v>-1.3758</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3065</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4572</v>
+        <v>-0.6041</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.4974</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3299</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.1444</v>
+        <v>0.1142</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8358</v>
+        <v>-0.261</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3087</v>
+        <v>0.3751</v>
       </c>
       <c r="V22" t="n">
-        <v>1.7513</v>
+        <v>0.5838</v>
       </c>
       <c r="W22" t="n">
-        <v>2.9188</v>
+        <v>0.5838</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8922</v>
+        <v>-2.577</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4149</v>
+        <v>-0.9863</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4773</v>
+        <v>-1.5906</v>
       </c>
       <c r="G23" t="n">
         <v>1.8839</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1112</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8482</v>
+        <v>-0.4195</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.263</v>
+        <v>-0.3764</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1675</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.3515</v>
+        <v>-5.8323</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1395</v>
+        <v>-0.8181</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.2119</v>
+        <v>-5.0143</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2962</v>
@@ -2326,13 +2326,13 @@
         <v>1.2487</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9284</v>
+        <v>-0.4092</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5219</v>
+        <v>-0.2005</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4064</v>
+        <v>-0.2087</v>
       </c>
       <c r="V24" t="n">
         <v>-4.0863</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.657</v>
+        <v>-11.9423</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8642000000000001</v>
+        <v>-0.8641000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.793</v>
+        <v>-11.078</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3665000000000007</v>
+        <v>0.3665000000000005</v>
       </c>
       <c r="H25" t="n">
-        <v>1.6116</v>
+        <v>1.611600000000001</v>
       </c>
       <c r="I25" t="n">
         <v>-1.245</v>
@@ -2404,13 +2404,13 @@
         <v>7.284199999999998</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.5534</v>
+        <v>-0.8380999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.85</v>
+        <v>-1.8499</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.703399999999999</v>
+        <v>1.0116</v>
       </c>
       <c r="V25" t="n">
         <v>-2.105</v>
